--- a/reports/predictions_2026-09-30_0950_betfair.xlsx
+++ b/reports/predictions_2026-09-30_0950_betfair.xlsx
@@ -326,7 +326,7 @@
     <t xml:space="preserve">Matched on the horse is estimated: the race's matched total shared by the runners' prices (the screenshots show the race's total, not each runner's). Borora Aura and Purrista sit near the GBP100 floor.</t>
   </si>
   <si>
-    <t xml:space="preserve">Near misses: Walsingham +2.9% and The Stone Power +2.7% (2:13 Musselburgh), Baila Morena +1.5%; Fan Club +5.1% and Redrosecastana +4.6% on too little money.</t>
+    <t xml:space="preserve">Expected CLV from 400,000 draws of the closing model per race. On the line: Walsingham +3.0% (2:13 Musselburgh; back only at 3.2 or better). The Stone Power clears at 7.2 only. Fan Club +5.4% and Redrosecastana +4.3% have too little money matched; Baila Morena +1.0%.</t>
   </si>
   <si>
     <t xml:space="preserve">Other races: no Betfair prices yet. Use the 'Rule: back at Betfair &gt;=' column on the runner sheets (the pre-registered rule, the model at least 22% shorter than Betfair), or send the race's screen and it will be scored the same way. In these five races the rule and the closing model picked the same five horses.</t>
@@ -9812,10 +9812,10 @@
         <v>1.13897388763537</v>
       </c>
       <c r="H7" s="13" t="n">
-        <v>1.1717967530627</v>
+        <v>1.17152760770667</v>
       </c>
       <c r="I7" s="15" t="n">
-        <v>-5.36187842816727E-005</v>
+        <v>0.0001761077053152</v>
       </c>
       <c r="J7" s="14" t="n">
         <v>7411.29838832091</v>
@@ -9860,10 +9860,10 @@
         <v>8.46359760629678</v>
       </c>
       <c r="H8" s="13" t="n">
-        <v>7.08430007799047</v>
+        <v>7.09730678608469</v>
       </c>
       <c r="I8" s="15" t="n">
-        <v>-0.0387084927593196</v>
+        <v>-0.0404701804536783</v>
       </c>
       <c r="J8" s="14" t="n">
         <v>1244.53618656709</v>
@@ -9908,10 +9908,10 @@
         <v>258.820549102596</v>
       </c>
       <c r="H9" s="13" t="n">
-        <v>183.402783405762</v>
+        <v>181.319999262412</v>
       </c>
       <c r="I9" s="15" t="n">
-        <v>-0.39933835063972</v>
+        <v>-0.392438678436461</v>
       </c>
       <c r="J9" s="14" t="n">
         <v>79.1654251120025</v>
@@ -9956,10 +9956,10 @@
         <v>3.85942742190114</v>
       </c>
       <c r="H10" s="13" t="n">
-        <v>2.0634304834173</v>
+        <v>2.06492694365435</v>
       </c>
       <c r="I10" s="15" t="n">
-        <v>-0.106959566763434</v>
+        <v>-0.107606756487271</v>
       </c>
       <c r="J10" s="14" t="n">
         <v>2767.9738041263</v>
@@ -10004,10 +10004,10 @@
         <v>2.07782336843758</v>
       </c>
       <c r="H11" s="18" t="n">
-        <v>3.12156890776029</v>
+        <v>3.10992610958305</v>
       </c>
       <c r="I11" s="20" t="n">
-        <v>0.0747687299983124</v>
+        <v>0.0787923996835877</v>
       </c>
       <c r="J11" s="19" t="n">
         <v>1513.1949712403</v>
@@ -10018,7 +10018,7 @@
       </c>
       <c r="L11" s="18" t="n">
         <f aca="false">IF(K11="BACK",(1+$B$2)*D11/(1+I11),"")</f>
-        <v>3.21045812340057</v>
+        <v>3.19848378706787</v>
       </c>
       <c r="M11" s="21" t="n">
         <f aca="false">IF(K11="BACK",$B$3/(D11-1),"")</f>
@@ -10052,10 +10052,10 @@
         <v>9.77248609421844</v>
       </c>
       <c r="H12" s="13" t="n">
-        <v>11.351964787714</v>
+        <v>11.40624832857</v>
       </c>
       <c r="I12" s="15" t="n">
-        <v>0.0145418036239786</v>
+        <v>0.0097134919950656</v>
       </c>
       <c r="J12" s="14" t="n">
         <v>417.672762797486</v>
@@ -10100,10 +10100,10 @@
         <v>9.3515560652692</v>
       </c>
       <c r="H13" s="18" t="n">
-        <v>14.5602428830734</v>
+        <v>14.5996933319891</v>
       </c>
       <c r="I13" s="20" t="n">
-        <v>0.169293251906119</v>
+        <v>0.166133655149338</v>
       </c>
       <c r="J13" s="19" t="n">
         <v>276.960154540437</v>
@@ -10114,7 +10114,7 @@
       </c>
       <c r="L13" s="18" t="n">
         <f aca="false">IF(K13="BACK",(1+$B$2)*D13/(1+I13),"")</f>
-        <v>14.9748576513686</v>
+        <v>15.0154314839302</v>
       </c>
       <c r="M13" s="21" t="n">
         <f aca="false">IF(K13="BACK",$B$3/(D13-1),"")</f>
@@ -10148,10 +10148,10 @@
         <v>26.5429346830437</v>
       </c>
       <c r="H14" s="18" t="n">
-        <v>36.6930299815512</v>
+        <v>36.9682192382985</v>
       </c>
       <c r="I14" s="20" t="n">
-        <v>0.146327883027151</v>
+        <v>0.137794685469391</v>
       </c>
       <c r="J14" s="19" t="n">
         <v>111.441539765286</v>
@@ -10162,7 +10162,7 @@
       </c>
       <c r="L14" s="18" t="n">
         <f aca="false">IF(K14="BACK",(1+$B$2)*D14/(1+I14),"")</f>
-        <v>37.7378938788104</v>
+        <v>38.0209193736507</v>
       </c>
       <c r="M14" s="21" t="n">
         <f aca="false">IF(K14="BACK",$B$3/(D14-1),"")</f>
@@ -10196,10 +10196,10 @@
         <v>78.837281568477</v>
       </c>
       <c r="H15" s="13" t="n">
-        <v>90.9534114391419</v>
+        <v>91.2890105873837</v>
       </c>
       <c r="I15" s="15" t="n">
-        <v>0.0460387037009994</v>
+        <v>0.0421932277151035</v>
       </c>
       <c r="J15" s="14" t="n">
         <v>53.756767530195</v>
@@ -10244,10 +10244,10 @@
         <v>2.24576382152965</v>
       </c>
       <c r="H16" s="13" t="n">
-        <v>2.46695424808457</v>
+        <v>2.47919433052588</v>
       </c>
       <c r="I16" s="15" t="n">
-        <v>-0.0419370415844098</v>
+        <v>-0.04666711435466</v>
       </c>
       <c r="J16" s="14" t="n">
         <v>575.021461476494</v>
@@ -10292,10 +10292,10 @@
         <v>7.56865875087695</v>
       </c>
       <c r="H17" s="13" t="n">
-        <v>6.02844151573524</v>
+        <v>5.97890041644682</v>
       </c>
       <c r="I17" s="15" t="n">
-        <v>-0.136143842530475</v>
+        <v>-0.128985940460325</v>
       </c>
       <c r="J17" s="14" t="n">
         <v>254.488703681366</v>
@@ -10340,10 +10340,10 @@
         <v>6.35280179535289</v>
       </c>
       <c r="H18" s="13" t="n">
-        <v>6.39306112610431</v>
+        <v>6.36836750147224</v>
       </c>
       <c r="I18" s="15" t="n">
-        <v>-0.0600915910252888</v>
+        <v>-0.0564470548966231</v>
       </c>
       <c r="J18" s="14" t="n">
         <v>216.908977755046</v>
@@ -10388,10 +10388,10 @@
         <v>8.04126964425935</v>
       </c>
       <c r="H19" s="18" t="n">
-        <v>10.3224586267639</v>
+        <v>10.3709958564623</v>
       </c>
       <c r="I19" s="20" t="n">
-        <v>0.164236569751896</v>
+        <v>0.158787833816464</v>
       </c>
       <c r="J19" s="19" t="n">
         <v>113.125882359259</v>
@@ -10402,7 +10402,7 @@
       </c>
       <c r="L19" s="18" t="n">
         <f aca="false">IF(K19="BACK",(1+$B$2)*D19/(1+I19),"")</f>
-        <v>10.6163990387572</v>
+        <v>10.6663184055811</v>
       </c>
       <c r="M19" s="21" t="n">
         <f aca="false">IF(K19="BACK",$B$3/(D19-1),"")</f>
@@ -10436,10 +10436,10 @@
         <v>15.3445452715334</v>
       </c>
       <c r="H20" s="13" t="n">
-        <v>13.3734865284307</v>
+        <v>13.4326992161349</v>
       </c>
       <c r="I20" s="15" t="n">
-        <v>-0.101372420910519</v>
+        <v>-0.105333661562659</v>
       </c>
       <c r="J20" s="14" t="n">
         <v>106.893911274053</v>
@@ -10484,10 +10484,10 @@
         <v>59.0350146639251</v>
       </c>
       <c r="H21" s="13" t="n">
-        <v>31.696633782832</v>
+        <v>31.0964249453056</v>
       </c>
       <c r="I21" s="15" t="n">
-        <v>-0.336487217084457</v>
+        <v>-0.32368039968284</v>
       </c>
       <c r="J21" s="14" t="n">
         <v>65.9763544005482</v>
@@ -10532,10 +10532,10 @@
         <v>19.4243743693351</v>
       </c>
       <c r="H22" s="13" t="n">
-        <v>20.0087809269315</v>
+        <v>19.9282627999552</v>
       </c>
       <c r="I22" s="15" t="n">
-        <v>0.0510946052687364</v>
+        <v>0.0553414465383772</v>
       </c>
       <c r="J22" s="14" t="n">
         <v>65.9763544005482</v>
@@ -10580,10 +10580,10 @@
         <v>327.876551957529</v>
       </c>
       <c r="H23" s="13" t="n">
-        <v>110.989133988817</v>
+        <v>111.010906728295</v>
       </c>
       <c r="I23" s="15" t="n">
-        <v>-0.602977284645287</v>
+        <v>-0.603055153319661</v>
       </c>
       <c r="J23" s="14" t="n">
         <v>31.4887146002616</v>
@@ -10628,10 +10628,10 @@
         <v>239.02932946811</v>
       </c>
       <c r="H24" s="13" t="n">
-        <v>98.4842208507545</v>
+        <v>98.5406061914588</v>
       </c>
       <c r="I24" s="15" t="n">
-        <v>-0.532227894746447</v>
+        <v>-0.532495555871604</v>
       </c>
       <c r="J24" s="14" t="n">
         <v>30.1196400524242</v>
@@ -10676,10 +10676,10 @@
         <v>2.75033571489615</v>
       </c>
       <c r="H25" s="13" t="n">
-        <v>3.06688694653424</v>
+        <v>3.06282024582441</v>
       </c>
       <c r="I25" s="15" t="n">
-        <v>0.0286222832929068</v>
+        <v>0.0299880503421816</v>
       </c>
       <c r="J25" s="14" t="n">
         <v>1273.77522680068</v>
@@ -10724,10 +10724,10 @@
         <v>7.91578802581519</v>
       </c>
       <c r="H26" s="13" t="n">
-        <v>5.02660191769758</v>
+        <v>5.04255941687002</v>
       </c>
       <c r="I26" s="15" t="n">
-        <v>-0.103436276151276</v>
+        <v>-0.106273508933006</v>
       </c>
       <c r="J26" s="14" t="n">
         <v>888.869268966616</v>
@@ -10772,10 +10772,10 @@
         <v>4.83747756158099</v>
       </c>
       <c r="H27" s="18" t="n">
-        <v>6.34267689006531</v>
+        <v>6.35221912995946</v>
       </c>
       <c r="I27" s="20" t="n">
-        <v>0.105270537704316</v>
+        <v>0.103610211383241</v>
       </c>
       <c r="J27" s="19" t="n">
         <v>561.898903202831</v>
@@ -10786,7 +10786,7 @@
       </c>
       <c r="L27" s="18" t="n">
         <f aca="false">IF(K27="BACK",(1+$B$2)*D27/(1+I27),"")</f>
-        <v>6.52328977751946</v>
+        <v>6.53310374046208</v>
       </c>
       <c r="M27" s="21" t="n">
         <f aca="false">IF(K27="BACK",$B$3/(D27-1),"")</f>
@@ -10798,51 +10798,51 @@
       </c>
     </row>
     <row r="28" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A28" s="12" t="s">
+      <c r="A28" s="17" t="s">
         <v>73</v>
       </c>
-      <c r="B28" s="12" t="s">
+      <c r="B28" s="17" t="s">
         <v>50</v>
       </c>
-      <c r="C28" s="12" t="s">
+      <c r="C28" s="17" t="s">
         <v>77</v>
       </c>
-      <c r="D28" s="13" t="n">
+      <c r="D28" s="18" t="n">
         <v>7.2</v>
       </c>
-      <c r="E28" s="14" t="n">
+      <c r="E28" s="19" t="n">
         <v>15</v>
       </c>
-      <c r="F28" s="13" t="n">
+      <c r="F28" s="18" t="n">
         <v>7.4</v>
       </c>
-      <c r="G28" s="13" t="n">
+      <c r="G28" s="18" t="n">
         <v>6.54447663110668</v>
       </c>
-      <c r="H28" s="13" t="n">
-        <v>7.02106098366246</v>
-      </c>
-      <c r="I28" s="15" t="n">
-        <v>0.0270057916597579</v>
-      </c>
-      <c r="J28" s="14" t="n">
+      <c r="H28" s="18" t="n">
+        <v>6.94675481458357</v>
+      </c>
+      <c r="I28" s="20" t="n">
+        <v>0.0379911895954774</v>
+      </c>
+      <c r="J28" s="19" t="n">
         <v>554.039790230686</v>
       </c>
-      <c r="K28" s="12" t="str">
+      <c r="K28" s="17" t="str">
         <f aca="false">IF(AND(I28&gt;=$B$2,J28&gt;=$B$4),"BACK","")</f>
-        <v/>
-      </c>
-      <c r="L28" s="13" t="str">
+        <v>BACK</v>
+      </c>
+      <c r="L28" s="18" t="n">
         <f aca="false">IF(K28="BACK",(1+$B$2)*D28/(1+I28),"")</f>
-        <v/>
-      </c>
-      <c r="M28" s="16" t="str">
+        <v>7.14456931266453</v>
+      </c>
+      <c r="M28" s="21" t="n">
         <f aca="false">IF(K28="BACK",$B$3/(D28-1),"")</f>
-        <v/>
-      </c>
-      <c r="N28" s="14" t="str">
+        <v>40.3225806451613</v>
+      </c>
+      <c r="N28" s="19" t="n">
         <f aca="false">IF(K28="BACK",M28*(D28-1),"")</f>
-        <v/>
+        <v>250</v>
       </c>
     </row>
     <row r="29" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -10868,10 +10868,10 @@
         <v>12.1057081104314</v>
       </c>
       <c r="H29" s="13" t="n">
-        <v>10.511722097066</v>
+        <v>10.5315423161211</v>
       </c>
       <c r="I29" s="15" t="n">
-        <v>-0.04727125012942</v>
+        <v>-0.0490642726474641</v>
       </c>
       <c r="J29" s="14" t="n">
         <v>394.66481921685</v>
@@ -10916,10 +10916,10 @@
         <v>14.7161313823327</v>
       </c>
       <c r="H30" s="13" t="n">
-        <v>12.5356851971294</v>
+        <v>12.6804947491371</v>
       </c>
       <c r="I30" s="15" t="n">
-        <v>-0.0812594086966473</v>
+        <v>-0.0917513032220602</v>
       </c>
       <c r="J30" s="14" t="n">
         <v>330.751991582334</v>
@@ -10964,10 +10964,10 @@
         <v>1.21232657103034</v>
       </c>
       <c r="H31" s="13" t="n">
-        <v>1.29769778224335</v>
+        <v>1.29670030148309</v>
       </c>
       <c r="I31" s="15" t="n">
-        <v>-0.0121760561945946</v>
+        <v>-0.0114161771559784</v>
       </c>
       <c r="J31" s="14" t="n">
         <v>1541.22496011269</v>
@@ -11012,10 +11012,10 @@
         <v>5.70972613153121</v>
       </c>
       <c r="H32" s="13" t="n">
-        <v>4.35911135267569</v>
+        <v>4.37040439460796</v>
       </c>
       <c r="I32" s="15" t="n">
-        <v>-0.0350729775511469</v>
+        <v>-0.0375663306466984</v>
       </c>
       <c r="J32" s="14" t="n">
         <v>462.775039887313</v>
